--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>19144.72</v>
+        <v>18931.42</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9874.200000000001</v>
+        <v>9764.190000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24535.36</v>
+        <v>24504.13</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10507.43</v>
+        <v>10621.72</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8349.700000000001</v>
+        <v>8440.52</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>49853.53</v>
+        <v>50212.95</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>62042.97</v>
+        <v>61932.94</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14339.89</v>
+        <v>14441.1</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8106.53</v>
+        <v>8025.87</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10779.15</v>
+        <v>10671.9</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10068.73</v>
+        <v>9952.200000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6368.01</v>
+        <v>6362.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17388.96</v>
+        <v>17575.49</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12754.04</v>
+        <v>12571.24</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21023.71</v>
+        <v>21343.78</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>40443.19</v>
+        <v>42229.25</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>28051.64</v>
+        <v>28866.44</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11675.27</v>
+        <v>11721.3</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>19440.79</v>
+        <v>19488.62</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5527.46</v>
+        <v>5550.29</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13333.36</v>
+        <v>13256.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11071.58</v>
+        <v>10780.03</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>19312.01</v>
+        <v>19549.68</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7825.47</v>
+        <v>7927.59</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39665.57</v>
+        <v>39427.84</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8873.24</v>
+        <v>8921.02</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11664.78</v>
+        <v>11753.14</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7570.42</v>
+        <v>7607.61</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>11227.9</v>
+        <v>11283.05</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7613.9</v>
+        <v>7637.44</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8856.33</v>
+        <v>8918.309999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>18197.5</v>
+        <v>18324.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Los Lagos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>507428-3919-CM25</t>
+          <t>1071775-2-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18931.42</v>
+        <v>27796.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>507428-3930-CM25</t>
+          <t>1393093-26-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9764.190000000001</v>
+        <v>21799.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>752-460-CM25</t>
+          <t>4180-30-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24504.13</v>
+        <v>7712.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2297-1628-CM25</t>
+          <t>696954-10-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10621.72</v>
+        <v>23451.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3888-661-CM25</t>
+          <t>1057536-2100-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8440.52</v>
+        <v>12583.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>507428-3993-CM25</t>
+          <t>2324-533-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>50212.95</v>
+        <v>26749.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>507428-3992-CM25</t>
+          <t>1057536-2102-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>61932.94</v>
+        <v>8943.030000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2854-1691-CM25</t>
+          <t>1071775-34-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14441.1</v>
+        <v>37145.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2852-1266-CM25</t>
+          <t>2852-325-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Ortopedic</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.765.630-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8025.87</v>
+        <v>10478.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2852-1271-CM25</t>
+          <t>1224953-263-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOC MUEBLES SANTA ANA LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.624.270-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10671.9</v>
+        <v>9368.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2852-1307-CM25</t>
+          <t>2181-114-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,28 +1179,28 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9952.200000000001</v>
+        <v>10562.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2181-334-CM25</t>
+          <t>1393093-437-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6362.89</v>
+        <v>19235.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1208107-103-CM25</t>
+          <t>2332-645-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17575.49</v>
+        <v>8394.299999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5413-1-CM26</t>
+          <t>507428-3111-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12571.24</v>
+        <v>7160.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1393093-15-CM26</t>
+          <t>507428-3037-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1423,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21343.78</v>
+        <v>10083.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1007793-42-CM26</t>
+          <t>507428-3112-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.999.290-3</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1484,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>42229.25</v>
+        <v>7160.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2328-156-CM26</t>
+          <t>2324-926-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,28 +1545,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>28866.44</v>
+        <v>21629.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2328-163-CM26</t>
+          <t>1787-42-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.804.018-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,28 +1606,28 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11721.3</v>
+        <v>13618.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5413-119-CM26</t>
+          <t>2328-725-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>19488.62</v>
+        <v>11345.98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5413-149-CM26</t>
+          <t>1071775-78-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5550.29</v>
+        <v>6525.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4180-52-CM26</t>
+          <t>507428-3246-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL LLICANCO SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.956.267-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13256.77</v>
+        <v>41836.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2852-216-CM26</t>
+          <t>2324-1125-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,28 +1850,28 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10780.03</v>
+        <v>6970.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>507428-373-CM26</t>
+          <t>2852-696-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,28 +1911,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>19549.68</v>
+        <v>14433.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5413-317-CM26</t>
+          <t>1079639-744-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,28 +1972,28 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7927.59</v>
+        <v>28134.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057922-24-CM26</t>
+          <t>1180842-38-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39427.84</v>
+        <v>499470.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1224953-321-CM26</t>
+          <t>4180-152-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,28 +2094,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8921.02</v>
+        <v>25899.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2328-455-CM26</t>
+          <t>1057922-139-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,43 +2155,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11753.14</v>
+        <v>111889.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2328-549-CM26</t>
+          <t>1057922-138-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7607.61</v>
+        <v>131578.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2328-554-CM26</t>
+          <t>507428-3930-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>11283.05</v>
+        <v>9764.190000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057922-25-CM26</t>
+          <t>507428-3919-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7637.44</v>
+        <v>18931.42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>507428-711-CM26</t>
+          <t>752-460-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8918.309999999999</v>
+        <v>24504.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2324-947-CM26</t>
+          <t>2297-1628-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2460,2020 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>10621.72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3888-661-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>8440.52</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>507428-3993-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>50212.95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>507428-3992-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>61932.94</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2854-1691-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>14441.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2852-1266-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>8025.87</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2852-1271-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>10671.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2852-1307-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>9952.200000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2181-334-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>6362.89</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1208107-103-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>17575.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5413-1-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>12571.24</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1393093-15-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>21343.78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1007793-42-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.999.290-3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>42229.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2328-156-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>28866.44</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2328-163-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>11721.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5413-119-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>19488.62</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5413-149-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>5550.29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4180-52-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>COMERCIAL LLICANCO SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.956.267-2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>13256.77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2852-216-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>10780.03</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>507428-373-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>GOOD HOSPITAL SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.367.722-0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>19549.68</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5413-317-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>7927.59</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1057922-24-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>39427.84</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1224953-321-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>71.420.700-8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>8921.02</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2328-455-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>11753.14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2328-549-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>7607.61</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2328-554-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>11283.05</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1057922-25-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>7637.44</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>507428-711-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>GOOD HOSPITAL SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.367.722-0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>8918.309999999999</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2324-947-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
         <v>18324.85</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2306-639-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>20053.4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2852-804-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>6536.01</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>507428-878-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>55525</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2852-848-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>8793.07</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1071775-128-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>12738.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>507428-3111-CM25</t>
+          <t>507428-3112-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>507428-3037-CM25</t>
+          <t>507428-3111-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10083.3</v>
+        <v>7160.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>507428-3112-CM25</t>
+          <t>507428-3037-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7160.27</v>
+        <v>10083.3</v>
       </c>
     </row>
     <row r="18">
@@ -2039,7 +2039,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4180-152-CM25</t>
+          <t>1057922-138-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25899.08</v>
+        <v>131578.76</v>
       </c>
     </row>
     <row r="28">
@@ -2161,7 +2161,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057922-138-CM25</t>
+          <t>4180-152-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>131578.76</v>
+        <v>25899.08</v>
       </c>
     </row>
     <row r="30">
@@ -2405,7 +2405,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2297-1628-CM25</t>
+          <t>3888-661-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.251.800-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>10621.72</v>
+        <v>8440.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3888-661-CM25</t>
+          <t>2297-1628-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.251.800-4</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8440.52</v>
+        <v>10621.72</v>
       </c>
     </row>
     <row r="35">
@@ -3442,7 +3442,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4180-52-CM26</t>
+          <t>1456840-15-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL LLICANCO SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.956.267-2</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13256.77</v>
+        <v>12814.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2852-216-CM26</t>
+          <t>4180-52-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL LLICANCO SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.956.267-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10780.03</v>
+        <v>13256.77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>507428-373-CM26</t>
+          <t>2852-216-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>19549.68</v>
+        <v>10780.03</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5413-317-CM26</t>
+          <t>507428-373-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.367.722-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7927.59</v>
+        <v>19549.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057922-24-CM26</t>
+          <t>5413-317-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>39427.84</v>
+        <v>7927.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1224953-321-CM26</t>
+          <t>1057922-24-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>71.420.700-8</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8921.02</v>
+        <v>39427.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2328-455-CM26</t>
+          <t>1224953-321-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>71.420.700-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORP MUNICIP ANCUD PARA LA EDUCAC SALUD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11753.14</v>
+        <v>8921.02</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2328-549-CM26</t>
+          <t>2328-455-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7607.61</v>
+        <v>11753.14</v>
       </c>
     </row>
     <row r="58">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057922-25-CM26</t>
+          <t>2328-549-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7637.44</v>
+        <v>7607.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>507428-711-CM26</t>
+          <t>1057922-25-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GOOD HOSPITAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.367.722-0</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8918.309999999999</v>
+        <v>7637.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2324-947-CM26</t>
+          <t>507428-711-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>GOOD HOSPITAL SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.367.722-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>18324.85</v>
+        <v>8918.309999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2306-639-CM26</t>
+          <t>2324-947-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>20053.4</v>
+        <v>18324.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2852-804-CM26</t>
+          <t>2306-639-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6536.01</v>
+        <v>20053.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>507428-878-CM26</t>
+          <t>2852-804-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>55525</v>
+        <v>6536.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2852-848-CM26</t>
+          <t>507428-878-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8793.07</v>
+        <v>55525</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1071775-128-CM26</t>
+          <t>2852-848-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,7 +4473,373 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
+        <v>8793.07</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1071775-128-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
         <v>12738.66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2852-889-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>7862.83</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>507428-898-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>13119.84</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>507428-915-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>22190.26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>507428-935-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.749.210-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>18683.27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>507428-891-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.979.210-6</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Plusmedical SpA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.520.087-3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>29443</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -562,7 +562,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2472,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2537,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2602,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2667,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2732,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2797,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2862,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2927,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3118,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3370,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3496,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3626,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3813,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3878,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3943,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4008,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4073,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4260,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4325,11 @@
           <t>77.367.722-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4451,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4516,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4703,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4768,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4090,7 +4090,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2328-554-CM26</t>
+          <t>2328-549-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11283.05</v>
+        <v>7607.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2328-549-CM26</t>
+          <t>2328-554-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7607.61</v>
+        <v>11283.05</v>
       </c>
     </row>
     <row r="60">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>507428-898-CM26</t>
+          <t>507428-915-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4840,13 +4840,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13119.84</v>
+        <v>22190.26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>507428-915-CM26</t>
+          <t>507428-898-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>22190.26</v>
+        <v>13119.84</v>
       </c>
     </row>
     <row r="71">
@@ -5024,6 +5024,67 @@
       </c>
       <c r="M72" s="2" t="n">
         <v>29443</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1057922-69-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.607.600-0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OSORNO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>149242.35</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/los-lagos.xlsx
@@ -3915,7 +3915,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
